--- a/public/documents/pieces-reponse-1/R1-coefficients-et-extrapolation.xlsx
+++ b/public/documents/pieces-reponse-1/R1-coefficients-et-extrapolation.xlsx
@@ -992,7 +992,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
@@ -1151,7 +1151,7 @@
     <row r="9">
       <c r="A9" s="4" t="inlineStr">
         <is>
-          <t>Les deux facons d'appliquer un taux de perte de 15 % au coefficient de 3,85 (reponse du 04/09/2026, p. 59 et p. 93)</t>
+          <t>Du coefficient sur achat revendu au coefficient sur la TOTALITE des achats : le calcul du service (reponse du 04/09/2026, p. 59 et p. 93) et le meme calcul avec la part revendue mesuree</t>
         </is>
       </c>
       <c r="B9" s="4" t="n"/>
@@ -1164,27 +1164,27 @@
     <row r="10">
       <c r="A10" s="4" t="inlineStr">
         <is>
-          <t>Methode</t>
+          <t>Lecture</t>
         </is>
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Ce sur quoi porte l'abattement</t>
+          <t>Part des achats supposee ou mesuree revendue</t>
         </is>
       </c>
       <c r="C10" s="4" t="inlineStr">
         <is>
-          <t>Cout retenu au denominateur</t>
+          <t>Coefficient sur achat revendu</t>
         </is>
       </c>
       <c r="D10" s="4" t="inlineStr">
         <is>
-          <t>CA retenu au numerateur</t>
+          <t>Coefficient sur la totalite des achats (produit des deux colonnes precedentes)</t>
         </is>
       </c>
       <c r="E10" s="4" t="inlineStr">
         <is>
-          <t>Coefficient obtenu</t>
+          <t>CA alcool que cela implique pour 107 924 € d'achats</t>
         </is>
       </c>
       <c r="F10" s="4" t="n"/>
@@ -1193,63 +1193,85 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A - calcul du service : 3,85 x (1-0,15)</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>sur le RESULTAT : le denominateur ne bouge pas, ce qui revient a amputer de 15 % le chiffre d'affaires encaisse</t>
-        </is>
-      </c>
-      <c r="C11" s="2" t="n">
-        <v>66723.48973827904</v>
-      </c>
-      <c r="D11" s="2" t="n">
-        <v>218352.6201685182</v>
-      </c>
-      <c r="E11" s="3" t="n">
+          <t>Service, p. 59 et 93 : 3,85 x (1-0,15) = 3,2725</t>
+        </is>
+      </c>
+      <c r="B11" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C11" s="3" t="n">
+        <v>3.85</v>
+      </c>
+      <c r="D11" s="3" t="n">
         <v>3.2725</v>
+      </c>
+      <c r="E11" s="2" t="n">
+        <v>353181.29</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>B - correction de la matiere</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>sur le DENOMINATEUR : si 15 % seulement des achats ne sont pas revendus, le cout des achats revendus passe de 61,8 % a 85 % des achats ; le CA encaisse est inchange</t>
-        </is>
-      </c>
-      <c r="C12" s="2" t="n">
-        <v>91735.39999999999</v>
-      </c>
-      <c r="D12" s="2" t="n">
+          <t>Le meme calcul sans l'arrondi du courrier (3,854864 au lieu de 3,85)</t>
+        </is>
+      </c>
+      <c r="B12" s="7" t="n">
+        <v>0.85</v>
+      </c>
+      <c r="C12" s="3" t="n">
+        <v>3.854863722040004</v>
+      </c>
+      <c r="D12" s="3" t="n">
+        <v>3.276634163734003</v>
+      </c>
+      <c r="E12" s="2" t="n">
+        <v>353627.4654868286</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>Part revendue MESUREE (cascade des 10 622 L : 6 567 L revendus)</t>
+        </is>
+      </c>
+      <c r="B13" s="7" t="n">
+        <v>0.6182451515722086</v>
+      </c>
+      <c r="C13" s="3" t="n">
+        <v>3.854863722040004</v>
+      </c>
+      <c r="D13" s="3" t="n">
+        <v>2.38325080612283</v>
+      </c>
+      <c r="E13" s="2" t="n">
         <v>257209.9600000003</v>
       </c>
-      <c r="E12" s="3" t="n">
-        <v>2.803824477791565</v>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" s="4" t="inlineStr">
-        <is>
-          <t>Ecart entre les deux methodes</t>
-        </is>
-      </c>
-      <c r="B13" s="4" t="inlineStr"/>
-      <c r="C13" s="5" t="n">
-        <v>25011.91026172096</v>
-      </c>
-      <c r="D13" s="5" t="n">
-        <v>38857.33983148215</v>
-      </c>
-      <c r="E13" s="6" t="n">
-        <v>-0.4686755222084349</v>
-      </c>
-      <c r="F13" s="4" t="n"/>
-      <c r="G13" s="4" t="n"/>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="inlineStr">
+        <is>
+          <t>Ecart entre le repere du service et la mesure</t>
+        </is>
+      </c>
+      <c r="B14" s="8" t="n">
+        <v>0.2317548484277914</v>
+      </c>
+      <c r="C14" s="6" t="inlineStr"/>
+      <c r="D14" s="6" t="n">
+        <v>0.8892491938771698</v>
+      </c>
+      <c r="E14" s="5" t="n">
+        <v>95971.32999999968</v>
+      </c>
+      <c r="F14" s="4" t="n"/>
+      <c r="G14" s="4" t="n"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Controle d'identite : le coefficient sur la totalite des achats est, par construction, le produit du coefficient sur achat revendu par la part des achats effectivement revendue. Sur les donnees mesurees : 3.854864 x 0.6182452 = 2.383251, soit exactement le coefficient sur la totalite des achats de la ligne GLOBALISE ci-dessus (2.383251). L'operation du service, 3,85 x (1-0,15), est donc exacte dans sa FORME : elle applique la meme identite avec une part revendue de 85 %. Tout l'ecart entre 3,2725 et 2,383251 tient a cette part supposee, non a l'arithmetique.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
@@ -1262,19 +1284,22 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J5"/>
+  <dimension ref="A1:M8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="13" customWidth="1" min="1" max="1"/>
     <col width="20" customWidth="1" min="2" max="2"/>
-    <col width="18" customWidth="1" min="3" max="3"/>
-    <col width="16" customWidth="1" min="4" max="4"/>
-    <col width="15" customWidth="1" min="5" max="5"/>
-    <col width="18" customWidth="1" min="6" max="6"/>
-    <col width="20" customWidth="1" min="7" max="7"/>
-    <col width="15" customWidth="1" min="8" max="8"/>
+    <col width="15" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="18" customWidth="1" min="7" max="7"/>
+    <col width="18" customWidth="1" min="8" max="8"/>
     <col width="18" customWidth="1" min="9" max="9"/>
-    <col width="20" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="10" max="10"/>
+    <col width="18" customWidth="1" min="11" max="11"/>
+    <col width="18" customWidth="1" min="12" max="12"/>
+    <col width="18" customWidth="1" min="13" max="13"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -1290,42 +1315,57 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>CA declare</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>CA reconstitue par le service</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>Coefficient declare</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>Coefficient reconstitue</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
-        <is>
-          <t>Repere methode A (3,2725)</t>
-        </is>
-      </c>
-      <c r="F1" s="1" t="inlineStr">
-        <is>
-          <t>CA correspondant au repere A</t>
-        </is>
-      </c>
       <c r="G1" s="1" t="inlineStr">
         <is>
-          <t>Exces du CA reconstitue sur le repere A</t>
+          <t>Repere du service (3,2725 : part revendue supposee de 85 %)</t>
         </is>
       </c>
       <c r="H1" s="1" t="inlineStr">
         <is>
-          <t>Repere methode B</t>
+          <t>CA correspondant au repere du service</t>
         </is>
       </c>
       <c r="I1" s="1" t="inlineStr">
         <is>
-          <t>CA correspondant au repere B</t>
+          <t>Ecart du CA reconstitue au repere du service</t>
         </is>
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Exces du CA reconstitue sur le repere B</t>
+          <t>Repere mesure (2,383251 : part revendue mesuree de 61,82 %)</t>
+        </is>
+      </c>
+      <c r="K1" s="1" t="inlineStr">
+        <is>
+          <t>CA correspondant au repere mesure</t>
+        </is>
+      </c>
+      <c r="L1" s="1" t="inlineStr">
+        <is>
+          <t>Ecart du CA reconstitue au repere mesure</t>
+        </is>
+      </c>
+      <c r="M1" s="1" t="inlineStr">
+        <is>
+          <t>Ecart du CA declare au repere mesure</t>
         </is>
       </c>
     </row>
@@ -1339,28 +1379,37 @@
         <v>175437</v>
       </c>
       <c r="C2" s="2" t="n">
+        <v>404031</v>
+      </c>
+      <c r="D2" s="2" t="n">
         <v>597265</v>
       </c>
-      <c r="D2" s="3" t="n">
+      <c r="E2" s="3" t="n">
+        <v>2.302997657278681</v>
+      </c>
+      <c r="F2" s="3" t="n">
         <v>3.4</v>
       </c>
-      <c r="E2" s="3" t="n">
+      <c r="G2" s="3" t="n">
         <v>3.2725</v>
       </c>
-      <c r="F2" s="2" t="n">
+      <c r="H2" s="2" t="n">
         <v>574117.5825</v>
       </c>
-      <c r="G2" s="2" t="n">
+      <c r="I2" s="2" t="n">
         <v>23147.41749999998</v>
       </c>
-      <c r="H2" s="3" t="n">
-        <v>2.803824477791565</v>
-      </c>
-      <c r="I2" s="2" t="n">
-        <v>491894.5549103188</v>
-      </c>
-      <c r="J2" s="2" t="n">
-        <v>105370.4450896812</v>
+      <c r="J2" s="3" t="n">
+        <v>2.38325080612283</v>
+      </c>
+      <c r="K2" s="2" t="n">
+        <v>418110.3716737709</v>
+      </c>
+      <c r="L2" s="2" t="n">
+        <v>179154.6283262291</v>
+      </c>
+      <c r="M2" s="2" t="n">
+        <v>-14079.37167377095</v>
       </c>
     </row>
     <row r="3">
@@ -1373,28 +1422,37 @@
         <v>183693</v>
       </c>
       <c r="C3" s="2" t="n">
+        <v>438658</v>
+      </c>
+      <c r="D3" s="2" t="n">
         <v>577522</v>
       </c>
-      <c r="D3" s="3" t="n">
+      <c r="E3" s="3" t="n">
+        <v>2.387995187622827</v>
+      </c>
+      <c r="F3" s="3" t="n">
         <v>3.14</v>
       </c>
-      <c r="E3" s="3" t="n">
+      <c r="G3" s="3" t="n">
         <v>3.2725</v>
       </c>
-      <c r="F3" s="2" t="n">
+      <c r="H3" s="2" t="n">
         <v>601135.3425</v>
       </c>
-      <c r="G3" s="2" t="n">
+      <c r="I3" s="2" t="n">
         <v>-23613.34250000003</v>
       </c>
-      <c r="H3" s="3" t="n">
-        <v>2.803824477791565</v>
-      </c>
-      <c r="I3" s="2" t="n">
-        <v>515042.929798966</v>
-      </c>
-      <c r="J3" s="2" t="n">
-        <v>62479.07020103402</v>
+      <c r="J3" s="3" t="n">
+        <v>2.38325080612283</v>
+      </c>
+      <c r="K3" s="2" t="n">
+        <v>437786.4903291211</v>
+      </c>
+      <c r="L3" s="2" t="n">
+        <v>139735.5096708789</v>
+      </c>
+      <c r="M3" s="2" t="n">
+        <v>871.5096708789351</v>
       </c>
     </row>
     <row r="4">
@@ -1407,28 +1465,37 @@
         <v>188539</v>
       </c>
       <c r="C4" s="2" t="n">
+        <v>435525</v>
+      </c>
+      <c r="D4" s="2" t="n">
         <v>575253</v>
       </c>
-      <c r="D4" s="3" t="n">
+      <c r="E4" s="3" t="n">
+        <v>2.309999522645182</v>
+      </c>
+      <c r="F4" s="3" t="n">
         <v>3.05</v>
       </c>
-      <c r="E4" s="3" t="n">
+      <c r="G4" s="3" t="n">
         <v>3.2725</v>
       </c>
-      <c r="F4" s="2" t="n">
+      <c r="H4" s="2" t="n">
         <v>616993.8774999999</v>
       </c>
-      <c r="G4" s="2" t="n">
+      <c r="I4" s="2" t="n">
         <v>-41740.87749999994</v>
       </c>
-      <c r="H4" s="3" t="n">
-        <v>2.803824477791565</v>
-      </c>
-      <c r="I4" s="2" t="n">
-        <v>528630.2632183438</v>
-      </c>
-      <c r="J4" s="2" t="n">
-        <v>46622.73678165616</v>
+      <c r="J4" s="3" t="n">
+        <v>2.38325080612283</v>
+      </c>
+      <c r="K4" s="2" t="n">
+        <v>449335.7237355923</v>
+      </c>
+      <c r="L4" s="2" t="n">
+        <v>125917.2762644077</v>
+      </c>
+      <c r="M4" s="2" t="n">
+        <v>-13810.72373559227</v>
       </c>
     </row>
     <row r="5">
@@ -1441,26 +1508,51 @@
         <v>547669</v>
       </c>
       <c r="C5" s="5" t="n">
+        <v>1278214</v>
+      </c>
+      <c r="D5" s="5" t="n">
         <v>1750040</v>
       </c>
-      <c r="D5" s="6" t="inlineStr"/>
       <c r="E5" s="6" t="n">
+        <v>2.333917019221464</v>
+      </c>
+      <c r="F5" s="6" t="n">
+        <v>3.195433738261614</v>
+      </c>
+      <c r="G5" s="6" t="n">
         <v>3.2725</v>
       </c>
-      <c r="F5" s="5" t="n">
+      <c r="H5" s="5" t="n">
         <v>1792246.8025</v>
       </c>
-      <c r="G5" s="5" t="n">
+      <c r="I5" s="5" t="n">
         <v>-42206.80249999999</v>
       </c>
-      <c r="H5" s="6" t="n">
-        <v>2.803824477791565</v>
-      </c>
-      <c r="I5" s="5" t="n">
-        <v>1535567.747927629</v>
-      </c>
-      <c r="J5" s="5" t="n">
-        <v>214472.2520723714</v>
+      <c r="J5" s="6" t="n">
+        <v>2.38325080612283</v>
+      </c>
+      <c r="K5" s="5" t="n">
+        <v>1305232.585738484</v>
+      </c>
+      <c r="L5" s="5" t="n">
+        <v>444807.4142615157</v>
+      </c>
+      <c r="M5" s="5" t="n">
+        <v>-27018.58573848428</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>Lecture. Colonnes 7 a 9 : le test de la page 93 tel que le service le pose. Globalement, le CA reconstitue est INFERIEUR de 42206 € a son propre repere : sur ce point precis, le courrier n'est pas pris en defaut, et la societe en convient. Le test n'est cependant pas reussi partout : sur 2022-2023, le CA reconstitue depasse le repere de 23147 €. Colonnes 10 a 13 : le meme test, la seule part revendue supposee (85 %) etant remplacee par la part mesuree (61,82 %). Le CA declare se situe alors a -27018 € du repere, soit -2.1 % ; le CA reconstitue le depasse de 444807 €, soit 34.1 %.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>Reserve de perimetre : le repere de la colonne 7 comme celui de la colonne 10 sont tires de l'ALCOOL seul (CA alcool TVA 20 % rapporte aux achats d'alcool), alors que les coefficients des colonnes 5 et 6 portent sur la TOTALITE des matieres, boisson et nourriture confondues. La confrontation est reprise ici telle que le service la construit page 93 ; elle suppose, sans le demontrer, que la nourriture supporte le meme coefficient que l'alcool.</t>
+        </is>
       </c>
     </row>
   </sheetData>

--- a/public/documents/pieces-reponse-1/R1-coefficients-et-extrapolation.xlsx
+++ b/public/documents/pieces-reponse-1/R1-coefficients-et-extrapolation.xlsx
@@ -1051,16 +1051,16 @@
         <v>35304.37449001761</v>
       </c>
       <c r="C2" s="7" t="n">
-        <v>0.6182451515722086</v>
+        <v>0.5903219732630389</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>21826.75835774295</v>
+        <v>20840.94801376449</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>81911.2000000001</v>
       </c>
       <c r="F2" s="3" t="n">
-        <v>3.752788144600613</v>
+        <v>3.930301056645864</v>
       </c>
       <c r="G2" s="3" t="n">
         <v>2.320143075276993</v>
@@ -1076,16 +1076,16 @@
         <v>36265.31901124417</v>
       </c>
       <c r="C3" s="7" t="n">
-        <v>0.6182451515722086</v>
+        <v>0.5903219732630389</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>22420.85764892115</v>
+        <v>21408.21467973126</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>88909.0100000001</v>
       </c>
       <c r="F3" s="3" t="n">
-        <v>3.965459813901376</v>
+        <v>4.153032437785522</v>
       </c>
       <c r="G3" s="3" t="n">
         <v>2.451626303698959</v>
@@ -1101,16 +1101,16 @@
         <v>36354.30649873823</v>
       </c>
       <c r="C4" s="7" t="n">
-        <v>0.6182451515722086</v>
+        <v>0.5903219732630389</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>22475.87373161495</v>
+        <v>21460.74594894447</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>86389.7500000001</v>
       </c>
       <c r="F4" s="3" t="n">
-        <v>3.843665925141892</v>
+        <v>4.025477502297589</v>
       </c>
       <c r="G4" s="3" t="n">
         <v>2.376327822482282</v>
@@ -1126,16 +1126,16 @@
         <v>107924</v>
       </c>
       <c r="C5" s="8" t="n">
-        <v>0.6182451515722086</v>
+        <v>0.5903219732630389</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>66723.48973827904</v>
+        <v>63709.90864244021</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>257209.9600000003</v>
       </c>
       <c r="F5" s="6" t="n">
-        <v>3.854863722040004</v>
+        <v>4.037204972990033</v>
       </c>
       <c r="G5" s="6" t="n">
         <v>2.38325080612283</v>
@@ -1212,33 +1212,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Le meme calcul sans l'arrondi du courrier (3,854864 au lieu de 3,85)</t>
+          <t>Le meme calcul sans l'arrondi du courrier (4,037205 au lieu de 3,85)</t>
         </is>
       </c>
       <c r="B12" s="7" t="n">
         <v>0.85</v>
       </c>
       <c r="C12" s="3" t="n">
-        <v>3.854863722040004</v>
+        <v>4.037204972990033</v>
       </c>
       <c r="D12" s="3" t="n">
-        <v>3.276634163734003</v>
+        <v>3.431624227041528</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>353627.4654868286</v>
+        <v>370354.6130792299</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Part revendue MESUREE (cascade des 10 622 L : 6 567 L revendus)</t>
+          <t>Part revendue MESUREE (cascade des 10 622 L : 6271 L revendus au verre et en cocktails, apres retrait des 296 L de contenance comptes deux fois)</t>
         </is>
       </c>
       <c r="B13" s="7" t="n">
-        <v>0.6182451515722086</v>
+        <v>0.5903219732630389</v>
       </c>
       <c r="C13" s="3" t="n">
-        <v>3.854863722040004</v>
+        <v>4.037204972990033</v>
       </c>
       <c r="D13" s="3" t="n">
         <v>2.38325080612283</v>
@@ -1254,7 +1254,7 @@
         </is>
       </c>
       <c r="B14" s="8" t="n">
-        <v>0.2317548484277914</v>
+        <v>0.2596780267369611</v>
       </c>
       <c r="C14" s="6" t="inlineStr"/>
       <c r="D14" s="6" t="n">
@@ -1269,7 +1269,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Controle d'identite : le coefficient sur la totalite des achats est, par construction, le produit du coefficient sur achat revendu par la part des achats effectivement revendue. Sur les donnees mesurees : 3.854864 x 0.6182452 = 2.383251, soit exactement le coefficient sur la totalite des achats de la ligne GLOBALISE ci-dessus (2.383251). L'operation du service, 3,85 x (1-0,15), est donc exacte dans sa FORME : elle applique la meme identite avec une part revendue de 85 %. Tout l'ecart entre 3,2725 et 2,383251 tient a cette part supposee, non a l'arithmetique.</t>
+          <t>Controle d'identite : le coefficient sur la totalite des achats est, par construction, le produit du coefficient sur achat revendu par la part des achats effectivement revendue. Sur les donnees mesurees : 4.037205 x 0.5903220 = 2.383251, soit exactement le coefficient sur la totalite des achats de la ligne GLOBALISE ci-dessus (2.383251). L'operation du service, 3,85 x (1-0,15), est donc exacte dans sa FORME : elle applique la meme identite avec une part revendue de 85 %. Tout l'ecart entre 3,2725 et 2,383251 tient a cette part supposee, non a l'arithmetique.</t>
         </is>
       </c>
     </row>

--- a/public/documents/pieces-reponse-1/R1-coefficients-et-extrapolation.xlsx
+++ b/public/documents/pieces-reponse-1/R1-coefficients-et-extrapolation.xlsx
@@ -20,10 +20,12 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="5">
     <numFmt numFmtId="164" formatCode="#,##0 &quot;€&quot;"/>
     <numFmt numFmtId="165" formatCode="#,##0.000"/>
     <numFmt numFmtId="166" formatCode="0.0 %"/>
+    <numFmt numFmtId="167" formatCode="0.00 %"/>
+    <numFmt numFmtId="168" formatCode="#,##0.000000"/>
   </numFmts>
   <fonts count="3">
     <font>
@@ -66,7 +68,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center" wrapText="1"/>
@@ -78,6 +80,10 @@
     <xf numFmtId="165" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="2" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="top" wrapText="1"/>
     </xf>
@@ -1050,7 +1056,7 @@
       <c r="B2" s="2" t="n">
         <v>35304.37449001761</v>
       </c>
-      <c r="C2" s="7" t="n">
+      <c r="C2" s="9" t="n">
         <v>0.5903219732630389</v>
       </c>
       <c r="D2" s="2" t="n">
@@ -1059,10 +1065,10 @@
       <c r="E2" s="2" t="n">
         <v>81911.2000000001</v>
       </c>
-      <c r="F2" s="3" t="n">
+      <c r="F2" s="10" t="n">
         <v>3.930301056645864</v>
       </c>
-      <c r="G2" s="3" t="n">
+      <c r="G2" s="10" t="n">
         <v>2.320143075276993</v>
       </c>
     </row>
@@ -1075,7 +1081,7 @@
       <c r="B3" s="2" t="n">
         <v>36265.31901124417</v>
       </c>
-      <c r="C3" s="7" t="n">
+      <c r="C3" s="9" t="n">
         <v>0.5903219732630389</v>
       </c>
       <c r="D3" s="2" t="n">
@@ -1084,10 +1090,10 @@
       <c r="E3" s="2" t="n">
         <v>88909.0100000001</v>
       </c>
-      <c r="F3" s="3" t="n">
+      <c r="F3" s="10" t="n">
         <v>4.153032437785522</v>
       </c>
-      <c r="G3" s="3" t="n">
+      <c r="G3" s="10" t="n">
         <v>2.451626303698959</v>
       </c>
     </row>
@@ -1100,7 +1106,7 @@
       <c r="B4" s="2" t="n">
         <v>36354.30649873823</v>
       </c>
-      <c r="C4" s="7" t="n">
+      <c r="C4" s="9" t="n">
         <v>0.5903219732630389</v>
       </c>
       <c r="D4" s="2" t="n">
@@ -1109,10 +1115,10 @@
       <c r="E4" s="2" t="n">
         <v>86389.7500000001</v>
       </c>
-      <c r="F4" s="3" t="n">
+      <c r="F4" s="10" t="n">
         <v>4.025477502297589</v>
       </c>
-      <c r="G4" s="3" t="n">
+      <c r="G4" s="10" t="n">
         <v>2.376327822482282</v>
       </c>
     </row>
@@ -1125,7 +1131,7 @@
       <c r="B5" s="5" t="n">
         <v>107924</v>
       </c>
-      <c r="C5" s="8" t="n">
+      <c r="C5" s="11" t="n">
         <v>0.5903219732630389</v>
       </c>
       <c r="D5" s="5" t="n">
@@ -1134,10 +1140,10 @@
       <c r="E5" s="5" t="n">
         <v>257209.9600000003</v>
       </c>
-      <c r="F5" s="6" t="n">
+      <c r="F5" s="12" t="n">
         <v>4.037204972990033</v>
       </c>
-      <c r="G5" s="6" t="n">
+      <c r="G5" s="12" t="n">
         <v>2.38325080612283</v>
       </c>
     </row>
@@ -1196,13 +1202,13 @@
           <t>Service, p. 59 et 93 : 3,85 x (1-0,15) = 3,2725</t>
         </is>
       </c>
-      <c r="B11" s="7" t="n">
+      <c r="B11" s="9" t="n">
         <v>0.85</v>
       </c>
-      <c r="C11" s="3" t="n">
+      <c r="C11" s="10" t="n">
         <v>3.85</v>
       </c>
-      <c r="D11" s="3" t="n">
+      <c r="D11" s="10" t="n">
         <v>3.2725</v>
       </c>
       <c r="E11" s="2" t="n">
@@ -1215,13 +1221,13 @@
           <t>Le meme calcul sans l'arrondi du courrier (4,037205 au lieu de 3,85)</t>
         </is>
       </c>
-      <c r="B12" s="7" t="n">
+      <c r="B12" s="9" t="n">
         <v>0.85</v>
       </c>
-      <c r="C12" s="3" t="n">
+      <c r="C12" s="10" t="n">
         <v>4.037204972990033</v>
       </c>
-      <c r="D12" s="3" t="n">
+      <c r="D12" s="10" t="n">
         <v>3.431624227041528</v>
       </c>
       <c r="E12" s="2" t="n">
@@ -1231,16 +1237,16 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Part revendue MESUREE (cascade des 10 622 L : 6271 L revendus au verre et en cocktails, apres retrait des 296 L de contenance comptes deux fois)</t>
-        </is>
-      </c>
-      <c r="B13" s="7" t="n">
+          <t>Part revendue MESUREE (cascade des 10 622 L : 6 271 L revendus au verre et en cocktails, apres retrait des 296 L de contenance comptes deux fois)</t>
+        </is>
+      </c>
+      <c r="B13" s="9" t="n">
         <v>0.5903219732630389</v>
       </c>
-      <c r="C13" s="3" t="n">
+      <c r="C13" s="10" t="n">
         <v>4.037204972990033</v>
       </c>
-      <c r="D13" s="3" t="n">
+      <c r="D13" s="10" t="n">
         <v>2.38325080612283</v>
       </c>
       <c r="E13" s="2" t="n">
@@ -1253,11 +1259,11 @@
           <t>Ecart entre le repere du service et la mesure</t>
         </is>
       </c>
-      <c r="B14" s="8" t="n">
+      <c r="B14" s="11" t="n">
         <v>0.2596780267369611</v>
       </c>
-      <c r="C14" s="6" t="inlineStr"/>
-      <c r="D14" s="6" t="n">
+      <c r="C14" s="12" t="inlineStr"/>
+      <c r="D14" s="12" t="n">
         <v>0.8892491938771698</v>
       </c>
       <c r="E14" s="5" t="n">
@@ -1269,7 +1275,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Controle d'identite : le coefficient sur la totalite des achats est, par construction, le produit du coefficient sur achat revendu par la part des achats effectivement revendue. Sur les donnees mesurees : 4.037205 x 0.5903220 = 2.383251, soit exactement le coefficient sur la totalite des achats de la ligne GLOBALISE ci-dessus (2.383251). L'operation du service, 3,85 x (1-0,15), est donc exacte dans sa FORME : elle applique la meme identite avec une part revendue de 85 %. Tout l'ecart entre 3,2725 et 2,383251 tient a cette part supposee, non a l'arithmetique.</t>
+          <t>Controle d'identite : le coefficient sur la totalite des achats est, par construction, le produit du coefficient sur achat revendu par la part des achats effectivement revendue. Sur les donnees mesurees : 4,037205 x 0,5903220 = 2,383251, soit exactement le coefficient sur la totalite des achats de la ligne GLOBALISE ci-dessus (2,383251). L'operation du service, 3,85 x (1-0,15), est donc exacte dans sa FORME : elle applique la meme identite avec une part revendue de 85 %. Tout l'ecart entre 3,2725 et 2,383251 tient a cette part supposee, non a l'arithmetique.</t>
         </is>
       </c>
     </row>
@@ -1350,7 +1356,7 @@
       </c>
       <c r="J1" s="1" t="inlineStr">
         <is>
-          <t>Repere mesure (2,383251 : part revendue mesuree de 61,82 %)</t>
+          <t>Repere calcule (2,383251 : part revendue de 59,03 %, poste par poste)</t>
         </is>
       </c>
       <c r="K1" s="1" t="inlineStr">
@@ -1544,7 +1550,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Lecture. Colonnes 7 a 9 : le test de la page 93 tel que le service le pose. Globalement, le CA reconstitue est INFERIEUR de 42206 € a son propre repere : sur ce point precis, le courrier n'est pas pris en defaut, et la societe en convient. Le test n'est cependant pas reussi partout : sur 2022-2023, le CA reconstitue depasse le repere de 23147 €. Colonnes 10 a 13 : le meme test, la seule part revendue supposee (85 %) etant remplacee par la part mesuree (61,82 %). Le CA declare se situe alors a -27018 € du repere, soit -2.1 % ; le CA reconstitue le depasse de 444807 €, soit 34.1 %.</t>
+          <t>Lecture. Colonnes 7 a 9 : le test de la page 93 tel que le service le pose. Globalement, le CA reconstitue est INFERIEUR de 42206 € a son propre repere : sur ce point precis, le courrier n'est pas pris en defaut, et la societe en convient. Le test n'est cependant pas reussi partout : sur 2022-2023, le CA reconstitue depasse le repere de 23147 €. Colonnes 10 a 13 : le meme test, la seule part revendue supposee (85 %) etant remplacee par la part mesuree (59,03 %). Le CA declare se situe alors a -27018 € du repere, soit -2.1 % ; le CA reconstitue le depasse de 444807 €, soit 34.1 %.</t>
         </is>
       </c>
     </row>
@@ -1566,7 +1572,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="46" customWidth="1" min="1" max="1"/>
@@ -1591,7 +1597,7 @@
           <t>CA liquides et CA cuisine reels</t>
         </is>
       </c>
-      <c r="B2" s="9" t="inlineStr">
+      <c r="B2" s="13" t="inlineStr">
         <is>
           <t>ANNEXE-D1/D2/D3, blocs LIQUIDE TVA 10 %, LIQUIDE TVA 20 %, SOLIDE TVA 10 % et lignes de total en bas de fichier</t>
         </is>
@@ -1603,7 +1609,7 @@
           <t>Rapport pour 1 € de CA liquide</t>
         </is>
       </c>
-      <c r="B3" s="9" t="inlineStr">
+      <c r="B3" s="13" t="inlineStr">
         <is>
           <t>ANNEXE-D1/D2/D3, derniere ligne « RAPPORT POUR 1 € DE CA LIQUIDE = ... C-A SOLIDE » (calcul du service)</t>
         </is>
@@ -1615,7 +1621,7 @@
           <t>Controle ligne a ligne</t>
         </is>
       </c>
-      <c r="B4" s="9" t="inlineStr">
+      <c r="B4" s="13" t="inlineStr">
         <is>
           <t>ANNEXE-C1/C2/C3, colonne 17 Tot_rem Ttc, agregee par reference produit et classee selon les blocs des annexes D</t>
         </is>
@@ -1627,7 +1633,7 @@
           <t>CA liquides reconstitue, coefficients 2,94 / 3,02 / 3,10, totaux reconstitues</t>
         </is>
       </c>
-      <c r="B5" s="9" t="inlineStr">
+      <c r="B5" s="13" t="inlineStr">
         <is>
           <t>Proposition de rectifications p. 52, tableau reproduit p. 90 de la reponse du 04/09/2026</t>
         </is>
@@ -1639,7 +1645,7 @@
           <t>Cout des matieres et coefficients reconstitues 3,40 / 3,14 / 3,05</t>
         </is>
       </c>
-      <c r="B6" s="9" t="inlineStr">
+      <c r="B6" s="13" t="inlineStr">
         <is>
           <t>Proposition de rectifications p. 34-35, tableau reproduit p. 56 de la reponse du 04/09/2026</t>
         </is>
@@ -1651,7 +1657,7 @@
           <t>Coefficient sur achat revendu 3,85 et taux de perte de 15 %</t>
         </is>
       </c>
-      <c r="B7" s="9" t="inlineStr">
+      <c r="B7" s="13" t="inlineStr">
         <is>
           <t>Reponse du 04/09/2026, p. 59, repris p. 93</t>
         </is>
@@ -1660,10 +1666,10 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Achats d'alcool 10 622 L / 107 924 € et cascade des volumes</t>
-        </is>
-      </c>
-      <c r="B8" s="9" t="inlineStr">
+          <t>Cout des achats d'alcool 107 924 €</t>
+        </is>
+      </c>
+      <c r="B8" s="13" t="inlineStr">
         <is>
           <t>src/data/boissonsPageData.json (scripts/rendu-final-*.py), factures fournisseur</t>
         </is>
@@ -1672,10 +1678,22 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
+          <t>Achats d'alcool 10 622 L et part revendue au verre et en cocktails (6 271 L, soit 59,03 %)</t>
+        </is>
+      </c>
+      <c r="B9" s="13" t="inlineStr">
+        <is>
+          <t>src/data/reponse1Calculs/cascade-10622.json, produit par scripts/reponse1-cascade-valeurs.py : source unique de la cascade, apres retrait des 296 L de contenance des articles mixtes comptes deux fois</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
           <t>Repartition des achats d'alcool par exercice</t>
         </is>
       </c>
-      <c r="B9" s="9" t="inlineStr">
+      <c r="B10" s="13" t="inlineStr">
         <is>
           <t>src/data/calculsBoissons/achatsBoissonsParPeriode.json (factures FCBS, categories biere, vin/cidre, spiritueux/liqueur)</t>
         </is>

--- a/public/documents/pieces-reponse-1/R1-coefficients-et-extrapolation.xlsx
+++ b/public/documents/pieces-reponse-1/R1-coefficients-et-extrapolation.xlsx
@@ -1057,16 +1057,16 @@
         <v>35304.37449001761</v>
       </c>
       <c r="C2" s="9" t="n">
-        <v>0.5903219732630389</v>
+        <v>0.607691583505931</v>
       </c>
       <c r="D2" s="2" t="n">
-        <v>20840.94801376449</v>
+        <v>21454.1712385252</v>
       </c>
       <c r="E2" s="2" t="n">
         <v>81911.2000000001</v>
       </c>
       <c r="F2" s="10" t="n">
-        <v>3.930301056645864</v>
+        <v>3.81796150917787</v>
       </c>
       <c r="G2" s="10" t="n">
         <v>2.320143075276993</v>
@@ -1082,16 +1082,16 @@
         <v>36265.31901124417</v>
       </c>
       <c r="C3" s="9" t="n">
-        <v>0.5903219732630389</v>
+        <v>0.607691583505931</v>
       </c>
       <c r="D3" s="2" t="n">
-        <v>21408.21467973126</v>
+        <v>22038.12913629071</v>
       </c>
       <c r="E3" s="2" t="n">
         <v>88909.0100000001</v>
       </c>
       <c r="F3" s="10" t="n">
-        <v>4.153032437785522</v>
+        <v>4.034326573283915</v>
       </c>
       <c r="G3" s="10" t="n">
         <v>2.451626303698959</v>
@@ -1107,16 +1107,16 @@
         <v>36354.30649873823</v>
       </c>
       <c r="C4" s="9" t="n">
-        <v>0.5903219732630389</v>
+        <v>0.607691583505931</v>
       </c>
       <c r="D4" s="2" t="n">
-        <v>21460.74594894447</v>
+        <v>22092.2060834782</v>
       </c>
       <c r="E4" s="2" t="n">
         <v>86389.7500000001</v>
       </c>
       <c r="F4" s="10" t="n">
-        <v>4.025477502297589</v>
+        <v>3.910417532480256</v>
       </c>
       <c r="G4" s="10" t="n">
         <v>2.376327822482282</v>
@@ -1132,16 +1132,16 @@
         <v>107924</v>
       </c>
       <c r="C5" s="11" t="n">
-        <v>0.5903219732630389</v>
+        <v>0.607691583505931</v>
       </c>
       <c r="D5" s="5" t="n">
-        <v>63709.90864244021</v>
+        <v>65584.5064582941</v>
       </c>
       <c r="E5" s="5" t="n">
         <v>257209.9600000003</v>
       </c>
       <c r="F5" s="12" t="n">
-        <v>4.037204972990033</v>
+        <v>3.921809797616803</v>
       </c>
       <c r="G5" s="12" t="n">
         <v>2.38325080612283</v>
@@ -1218,33 +1218,33 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Le meme calcul sans l'arrondi du courrier (4,037205 au lieu de 3,85)</t>
+          <t>Le meme calcul sans l'arrondi du courrier (3,921810 au lieu de 3,85)</t>
         </is>
       </c>
       <c r="B12" s="9" t="n">
         <v>0.85</v>
       </c>
       <c r="C12" s="10" t="n">
-        <v>4.037204972990033</v>
+        <v>3.921809797616803</v>
       </c>
       <c r="D12" s="10" t="n">
-        <v>3.431624227041528</v>
+        <v>3.333538327974283</v>
       </c>
       <c r="E12" s="2" t="n">
-        <v>370354.6130792299</v>
+        <v>359768.7905082965</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Part revendue MESUREE (cascade des 10 622 L : 6 271 L revendus au verre et en cocktails, apres retrait des 296 L de contenance comptes deux fois)</t>
+          <t>Part revendue MESUREE (cascade des 10 622 L : 6 455 L revendus au verre et en cocktails, apres retrait des 296 L de contenance comptes deux fois)</t>
         </is>
       </c>
       <c r="B13" s="9" t="n">
-        <v>0.5903219732630389</v>
+        <v>0.607691583505931</v>
       </c>
       <c r="C13" s="10" t="n">
-        <v>4.037204972990033</v>
+        <v>3.921809797616803</v>
       </c>
       <c r="D13" s="10" t="n">
         <v>2.38325080612283</v>
@@ -1260,7 +1260,7 @@
         </is>
       </c>
       <c r="B14" s="11" t="n">
-        <v>0.2596780267369611</v>
+        <v>0.242308416494069</v>
       </c>
       <c r="C14" s="12" t="inlineStr"/>
       <c r="D14" s="12" t="n">
@@ -1275,7 +1275,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>Controle d'identite : le coefficient sur la totalite des achats est, par construction, le produit du coefficient sur achat revendu par la part des achats effectivement revendue. Sur les donnees mesurees : 4,037205 x 0,5903220 = 2,383251, soit exactement le coefficient sur la totalite des achats de la ligne GLOBALISE ci-dessus (2,383251). L'operation du service, 3,85 x (1-0,15), est donc exacte dans sa FORME : elle applique la meme identite avec une part revendue de 85 %. Tout l'ecart entre 3,2725 et 2,383251 tient a cette part supposee, non a l'arithmetique.</t>
+          <t>Controle d'identite : le coefficient sur la totalite des achats est, par construction, le produit du coefficient sur achat revendu par la part des achats effectivement revendue. Sur les donnees mesurees : 3,921810 x 0,6076916 = 2,383251, soit exactement le coefficient sur la totalite des achats de la ligne GLOBALISE ci-dessus (2,383251). L'operation du service, 3,85 x (1-0,15), est donc exacte dans sa FORME : elle applique la meme identite avec une part revendue de 85 %. Tout l'ecart entre 3,2725 et 2,383251 tient a cette part supposee, non a l'arithmetique.</t>
         </is>
       </c>
     </row>
